--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484019_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484019_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.8347</v>
+        <v>9.0001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.8048</v>
+        <v>8.5214</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0298</v>
+        <v>0.4787</v>
       </c>
       <c r="G2" t="n">
         <v>3.7163</v>
@@ -610,13 +610,13 @@
         <v>2.7774</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.3854</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1758</v>
+        <v>-0.1076</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7267</v>
+        <v>-0.2778</v>
       </c>
       <c r="V2" t="n">
         <v>3.0902</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8174</v>
+        <v>7.1112</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8846</v>
+        <v>6.0943</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9328</v>
+        <v>1.017</v>
       </c>
       <c r="G3" t="n">
         <v>7.5115</v>
@@ -688,13 +688,13 @@
         <v>3.1741</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0459</v>
+        <v>0.248</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2382</v>
+        <v>0.4479</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2841</v>
+        <v>-0.1999</v>
       </c>
       <c r="V3" t="n">
         <v>0.1453</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3915</v>
+        <v>2.5045</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7415</v>
+        <v>1.8265</v>
       </c>
       <c r="F4" t="n">
-        <v>0.65</v>
+        <v>0.678</v>
       </c>
       <c r="G4" t="n">
         <v>1.1456</v>
@@ -766,13 +766,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1151</v>
+        <v>0.2282</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0056</v>
+        <v>0.0794</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1207</v>
+        <v>0.1488</v>
       </c>
       <c r="V4" t="n">
         <v>0.3373</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9414</v>
+        <v>1.7512</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9573</v>
+        <v>3.0197</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.016</v>
+        <v>-1.2685</v>
       </c>
       <c r="G5" t="n">
         <v>2.7494</v>
@@ -844,13 +844,13 @@
         <v>1.9838</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2794</v>
+        <v>0.0893</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2436</v>
+        <v>-0.1813</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5231</v>
+        <v>0.2706</v>
       </c>
       <c r="V5" t="n">
         <v>-1.881</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1332</v>
+        <v>-0.1097</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8055</v>
+        <v>-1.9643</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9388</v>
+        <v>1.8546</v>
       </c>
       <c r="G6" t="n">
         <v>-2.7147</v>
@@ -922,13 +922,13 @@
         <v>3.5709</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6864</v>
+        <v>0.4435</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4876</v>
+        <v>0.3288</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1989</v>
+        <v>0.1147</v>
       </c>
       <c r="V6" t="n">
         <v>2.5583</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7938</v>
+        <v>-0.3429</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7031</v>
+        <v>-1.9436</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9093</v>
+        <v>1.6007</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6747</v>
@@ -1000,13 +1000,13 @@
         <v>2.3806</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3872</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6121</v>
+        <v>0.1474</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2249</v>
+        <v>-0.0837</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1206</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MAJORAL DE LOS RIOS</t>
+          <t>G. GUTIÉRREZ MONREAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1292</v>
+        <v>-2.7611</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4393</v>
+        <v>-3.0513</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6898</v>
+        <v>0.2902</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2619</v>
+        <v>-3.8233</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4637</v>
+        <v>-0.1969</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7982</v>
+        <v>-3.6264</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9373</v>
+        <v>-2.5724</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3374</v>
+        <v>0.6653</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5999</v>
+        <v>-3.2378</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3246</v>
+        <v>-1.2509</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1263</v>
+        <v>-0.8623</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1983</v>
+        <v>-0.3886</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5952</v>
+        <v>2.579</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5952</v>
+        <v>2.579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2721</v>
+        <v>0.0269</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3117</v>
+        <v>-0.1416</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0396</v>
+        <v>0.1686</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.5437</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GUTIÉRREZ MONREAL</t>
+          <t>P. MAJORAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6649</v>
+        <v>-2.9251</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6465</v>
+        <v>-2.2353</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0184</v>
+        <v>-0.6898</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.8233</v>
+        <v>-2.2619</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1969</v>
+        <v>-0.4637</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.6264</v>
+        <v>-1.7982</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5724</v>
+        <v>-0.9373</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6653</v>
+        <v>-0.3374</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.2378</v>
+        <v>-0.5999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2509</v>
+        <v>-1.3246</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8623</v>
+        <v>-0.1263</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3886</v>
+        <v>-1.1983</v>
       </c>
       <c r="P9" t="n">
-        <v>2.579</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q9" t="n">
+        <v>-1.1903</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.5952</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.1077</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="V9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.579</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.8768</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.7368</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-1.5437</v>
-      </c>
       <c r="W9" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. IGLESIAS GARCIA</t>
+          <t>O. BESORA TOMAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.196</v>
+        <v>-3.5262</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3486</v>
+        <v>-2.5303</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1526</v>
+        <v>-0.996</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.8837</v>
+        <v>-2.1896</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8572</v>
+        <v>-2.5302</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0265</v>
+        <v>0.3406</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7689</v>
+        <v>-0.2174</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0658</v>
+        <v>-1.8793</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8347</v>
+        <v>1.6619</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1148</v>
+        <v>-1.9723</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.923</v>
+        <v>-0.6509</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1918</v>
+        <v>-1.3214</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3887</v>
+        <v>0.9919</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.1661</v>
+        <v>-2.1822</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7774</v>
+        <v>3.1741</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7509</v>
+        <v>-0.3982</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0544</v>
+        <v>-0.3967</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6965</v>
+        <v>-0.0015</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6745</v>
+        <v>-1.9303</v>
       </c>
       <c r="W10" t="n">
-        <v>0.532</v>
+        <v>0.266</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2065</v>
+        <v>-2.1963</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. BESORA TOMAS</t>
+          <t>A. IGLESIAS GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3371</v>
+        <v>-5.1462</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3692</v>
+        <v>-5.1025</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9679</v>
+        <v>-0.0438</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1896</v>
+        <v>-3.8837</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5302</v>
+        <v>-0.8572</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3406</v>
+        <v>-3.0265</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2174</v>
+        <v>-1.7689</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8793</v>
+        <v>0.0658</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6619</v>
+        <v>-1.8347</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9723</v>
+        <v>-2.1148</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6509</v>
+        <v>-0.923</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3214</v>
+        <v>-1.1918</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9919</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1822</v>
+        <v>-4.1661</v>
       </c>
       <c r="R11" t="n">
-        <v>3.1741</v>
+        <v>2.7774</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.209</v>
+        <v>0.8006</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2356</v>
+        <v>0.3005</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0265</v>
+        <v>0.5001</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.9303</v>
+        <v>-0.6745</v>
       </c>
       <c r="W11" t="n">
-        <v>0.266</v>
+        <v>0.532</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1963</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.9972</v>
+        <v>5.555800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.075999999999997</v>
+        <v>2.6346</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9212</v>
+        <v>2.9211</v>
       </c>
       <c r="G12" t="n">
         <v>-1.425100000000001</v>
@@ -1390,16 +1390,16 @@
         <v>24.798</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5101000000000002</v>
+        <v>1.0486</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1894</v>
+        <v>0.3691</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6793999999999998</v>
+        <v>0.6795</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01900000000000013</v>
+        <v>-0.01900000000000002</v>
       </c>
       <c r="W12" t="n">
         <v>10.0933</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7441</v>
+        <v>3.9822</v>
       </c>
       <c r="E13" t="n">
-        <v>5.897</v>
+        <v>5.999</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1529</v>
+        <v>-2.0168</v>
       </c>
       <c r="G13" t="n">
         <v>4.4911</v>
@@ -1468,13 +1468,13 @@
         <v>1.9838</v>
       </c>
       <c r="S13" t="n">
-        <v>0.051</v>
+        <v>0.2891</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0566</v>
+        <v>0.0454</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1076</v>
+        <v>0.2436</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7979000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6573</v>
+        <v>2.0171</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3419</v>
+        <v>-0.2703</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3155</v>
+        <v>2.2874</v>
       </c>
       <c r="G14" t="n">
         <v>0.4359</v>
@@ -1546,13 +1546,13 @@
         <v>2.1822</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.1969</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6236</v>
+        <v>0.0114</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2136</v>
+        <v>0.1855</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7979000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2564</v>
+        <v>0.4196</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4396</v>
+        <v>0.3767</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1832</v>
+        <v>0.0429</v>
       </c>
       <c r="G15" t="n">
         <v>2.7558</v>
@@ -1624,13 +1624,13 @@
         <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2863</v>
+        <v>0.3897</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0485</v>
+        <v>-0.2323</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7622</v>
+        <v>0.6219</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9405</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3209</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="E16" t="n">
         <v>-0.6733</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3524</v>
+        <v>0.769</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9464</v>
@@ -1702,13 +1702,13 @@
         <v>2.1822</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1247</v>
+        <v>0.2919</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0566</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.06809999999999999</v>
+        <v>0.3485</v>
       </c>
       <c r="V16" t="n">
         <v>1.5437</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. HAGENAERS COS</t>
+          <t>S. CASAÚ PUEYO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.35</v>
+        <v>-0.0905</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1855</v>
+        <v>-2.0672</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5356</v>
+        <v>1.9767</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.0557</v>
+        <v>-0.0118</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3252</v>
+        <v>-0.8215</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7306</v>
+        <v>0.8097</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5165</v>
+        <v>0.3362</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3268</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8434</v>
+        <v>1.1723</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5723</v>
+        <v>-0.348</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9983</v>
+        <v>0.0147</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.574</v>
+        <v>-0.3626</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-2.3806</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9838</v>
+        <v>-5.9515</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9838</v>
+        <v>3.5709</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1781</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6528</v>
+        <v>-0.6744</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5253</v>
+        <v>-0.0398</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4724</v>
+        <v>3.0162</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4.2226</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CASAÚ PUEYO</t>
+          <t>E. GANDOL COBO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9611</v>
+        <v>-1.6188</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5773</v>
+        <v>-0.9543</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6162</v>
+        <v>-0.6645</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0118</v>
+        <v>-1.0676</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8215</v>
+        <v>0.0906</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8097</v>
+        <v>-1.1582</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3362</v>
+        <v>0.0603</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8362000000000001</v>
+        <v>0.0202</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1723</v>
+        <v>0.0402</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.348</v>
+        <v>-1.1279</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0147</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3626</v>
+        <v>-1.1983</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.3806</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.9515</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>3.5709</v>
+        <v>0.5952</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5848</v>
+        <v>-0.1545</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1846</v>
+        <v>-0.0227</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4003</v>
+        <v>-0.1318</v>
       </c>
       <c r="V18" t="n">
-        <v>3.0162</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.2226</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. GANDOL COBO</t>
+          <t>J. HAGENAERS COS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.805</v>
+        <v>-2.3591</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0563</v>
+        <v>-0.651</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7487</v>
+        <v>-1.7081</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0676</v>
+        <v>-2.0557</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0906</v>
+        <v>-1.3252</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1582</v>
+        <v>-0.7306</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0603</v>
+        <v>0.5165</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0202</v>
+        <v>-0.3268</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0402</v>
+        <v>0.8434</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1279</v>
+        <v>-2.5723</v>
       </c>
       <c r="N19" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.9983</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1983</v>
+        <v>-1.574</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3407</v>
+        <v>1.169</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1247</v>
+        <v>0.8163</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.216</v>
+        <v>0.3527</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.569</v>
+        <v>-2.6115</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8991</v>
+        <v>-1.7971</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.67</v>
+        <v>-0.8145</v>
       </c>
       <c r="G20" t="n">
         <v>0.4735</v>
@@ -2014,13 +2014,13 @@
         <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1814</v>
+        <v>-0.2239</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3117</v>
+        <v>-0.2097</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1303</v>
+        <v>-0.0142</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4724</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1363</v>
+        <v>-3.1517</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7001</v>
+        <v>-2.8839</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4361</v>
+        <v>-0.2678</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6496</v>
@@ -2092,13 +2092,13 @@
         <v>2.579</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0384</v>
+        <v>-0.0539</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1732</v>
+        <v>-0.357</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1348</v>
+        <v>0.3031</v>
       </c>
       <c r="V21" t="n">
         <v>0.9405</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.997299999999999</v>
+        <v>-3.317</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9213</v>
+        <v>-2.9214</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.076</v>
+        <v>-0.3956999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.4252</v>
@@ -2170,13 +2170,13 @@
         <v>18.8464</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5100000000000002</v>
+        <v>1.1901</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6794999999999999</v>
+        <v>-0.6796</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1894</v>
+        <v>1.8695</v>
       </c>
       <c r="V22" t="n">
         <v>0.01930000000000009</v>
